--- a/raw/AASTMT_CARBON_BUILD_PLAYBOOK.xlsx
+++ b/raw/AASTMT_CARBON_BUILD_PLAYBOOK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahmed\aast\carbon\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62564F1C-051D-4EF3-A45B-4DD8C240F0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25E5646-7BD8-4CED-BA79-E4F5E0E2D450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="857" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="857" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLAYBOOK" sheetId="1" r:id="rId1"/>
@@ -2216,25 +2216,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2249,6 +2237,18 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2557,17 +2557,17 @@
   <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" style="24" customWidth="1"/>
-    <col min="2" max="2" width="10" style="24" customWidth="1"/>
-    <col min="3" max="3" width="28" style="24" customWidth="1"/>
-    <col min="4" max="4" width="5" style="24" customWidth="1"/>
-    <col min="5" max="5" width="94.6640625" style="24" customWidth="1"/>
-    <col min="6" max="6" width="12" style="24" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="24"/>
+    <col min="1" max="1" width="6" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10" style="15" customWidth="1"/>
+    <col min="3" max="3" width="28" style="15" customWidth="1"/>
+    <col min="4" max="4" width="5" style="15" customWidth="1"/>
+    <col min="5" max="5" width="94.6640625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="12" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21" t="s">
@@ -2576,118 +2576,118 @@
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
       <c r="E1" s="22"/>
-      <c r="F1" s="23"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="25"/>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A5" s="25"/>
-      <c r="B5" s="26" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="26" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="21" t="s">
@@ -2696,64 +2696,64 @@
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
-      <c r="F10" s="23"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26" t="s">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B16" s="21" t="s">
@@ -2762,100 +2762,100 @@
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
-      <c r="F16" s="23"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26" t="s">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26" t="s">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="F19" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26" t="s">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26" t="s">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26" t="s">
+      <c r="A22" s="17"/>
+      <c r="B22" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B24" s="21" t="s">
@@ -2864,46 +2864,46 @@
       <c r="C24" s="22"/>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
-      <c r="F24" s="23"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="26" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26" t="s">
+      <c r="A26" s="17"/>
+      <c r="B26" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="E26" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="25" t="s">
+      <c r="F26" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26" t="s">
+      <c r="A27" s="17"/>
+      <c r="B27" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="E27" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B29" s="21" t="s">
@@ -2912,95 +2912,95 @@
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
-      <c r="F29" s="23"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26" t="s">
+      <c r="A31" s="17"/>
+      <c r="B31" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="E31" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="25" t="s">
+      <c r="F31" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26" t="s">
+      <c r="A32" s="17"/>
+      <c r="B32" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="27" t="s">
+      <c r="D32" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="25" t="s">
+      <c r="E32" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F32" s="25" t="s">
+      <c r="F32" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A33" s="25"/>
-      <c r="B33" s="26" t="s">
+      <c r="A33" s="17"/>
+      <c r="B33" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="25" t="s">
+      <c r="E33" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F33" s="25" t="s">
+      <c r="F33" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A34" s="25"/>
-      <c r="B34" s="26" t="s">
+      <c r="A34" s="17"/>
+      <c r="B34" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E34" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F34" s="25" t="s">
+      <c r="F34" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="25"/>
-      <c r="B35" s="26" t="s">
+      <c r="A35" s="17"/>
+      <c r="B35" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="E35" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="F35" s="17" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       <c r="A38" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
@@ -3161,12 +3161,12 @@
       <c r="A48" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
@@ -3314,12 +3314,12 @@
       <c r="A58" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="28" t="s">
+      <c r="B58" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
@@ -3449,12 +3449,12 @@
       <c r="A67" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B67" s="28" t="s">
+      <c r="B67" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
@@ -3500,7 +3500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
       <c r="B71" s="13" t="s">
         <v>147</v>
@@ -3566,11 +3566,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="23" t="s">
         <v>480</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4274,11 +4274,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="25" t="s">
         <v>510</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4718,11 +4718,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>512</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5208,13 +5208,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="23" t="s">
         <v>514</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -5434,12 +5434,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="25" t="s">
         <v>536</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -5526,13 +5526,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="27" t="s">
         <v>548</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -6009,12 +6009,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="28" t="s">
         <v>617</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
